--- a/data/trans_orig/P24E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007 (tasa de respuesta: 98,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29295</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45797</t>
+          <t>46401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>44504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32309</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49885</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71993</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>37636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35866</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54115</t>
+          <t>55034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21458</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>32731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59260</t>
+          <t>60039</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56205</t>
+          <t>56871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45522</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72803</t>
+          <t>71532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97104</t>
+          <t>95898</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25481</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43377</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>43319</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>66949</t>
+          <t>66815</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>32426</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>53005</t>
+          <t>52790</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36255</t>
+          <t>36281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>60386</t>
+          <t>60094</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>84531</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>115310</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>155553</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>219819</t>
+          <t>220511</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>271533</t>
+          <t>268912</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>197991</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>238429</t>
+          <t>237532</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>332451</t>
+          <t>334467</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>388284</t>
+          <t>386100</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>70966</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>122082</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41838</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>66272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27771</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>46815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39182</t>
+          <t>38839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55875</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80772</t>
+          <t>80832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27249</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48678</t>
+          <t>48855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77109</t>
+          <t>78067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>30364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93287</t>
+          <t>92873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119701</t>
+          <t>119682</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,1%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18598</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52823</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>74,42%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>35207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19896</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>59513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>36714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23464</t>
+          <t>24031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40024</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>47392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>71053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14113</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>30996</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8391</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19044</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29843</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46299</t>
+          <t>46869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30844</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>51287</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,57%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34974</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>55854</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>54564</t>
+          <t>55921</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>76990</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106802</t>
+          <t>106412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44183</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>64928</t>
+          <t>65499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45176</t>
+          <t>44802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72407</t>
+          <t>74434</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102984</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>41332</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63658</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84249</t>
+          <t>83945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112398</t>
+          <t>113364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>44051</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>67566</t>
+          <t>66373</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>38895</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>70330</t>
+          <t>70977</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>99312</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>266205</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>201680</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>246549</t>
+          <t>246045</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>429150</t>
+          <t>428935</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>497431</t>
+          <t>497483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>271644</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>325231</t>
+          <t>325611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>180332</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>226940</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>466350</t>
+          <t>463343</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>534788</t>
+          <t>534896</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>102087</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016 (tasa de respuesta: 98,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27085</t>
+          <t>27247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>29448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45382</t>
+          <t>46424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>34722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>41495</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>57713</t>
+          <t>58411</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23104</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31048</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>45826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>23378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>27124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>45622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13119</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>28775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>45386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70525</t>
+          <t>69140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>45634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>28215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>45431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68870</t>
+          <t>69331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42158</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34765</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>42658</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57393</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17239</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55272</t>
+          <t>54733</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24085</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42581</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76733</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>14853</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>45195</t>
+          <t>43878</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>53961</t>
+          <t>52995</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75107</t>
+          <t>75126</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>68405</t>
+          <t>69827</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>107786</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>139035</t>
+          <t>138953</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32724</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51659</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>111933</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>151632</t>
+          <t>151715</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>228457</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>282473</t>
+          <t>285309</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>248920</t>
+          <t>250610</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>295590</t>
+          <t>296246</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>188023</t>
+          <t>188183</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>229106</t>
+          <t>228262</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>450321</t>
+          <t>446226</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>511905</t>
+          <t>508088</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>139632</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12090</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44504</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>49587</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71838</t>
+          <t>72281</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>15667</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23505</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37636</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19274</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>37364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20683</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27730</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>37363</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60039</t>
+          <t>60362</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38242</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>55996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>45073</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>71532</t>
+          <t>72012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95898</t>
+          <t>97133</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>44053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>66815</t>
+          <t>65915</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>52790</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>84531</t>
+          <t>82102</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,82 +4165,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>7665</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>14129</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>20810</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>12827</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>30593</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>8,75%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>7665</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>3023</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>14916</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>20810</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>12783</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>29527</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>115202</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>154693</t>
+          <t>152688</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>220511</t>
+          <t>217737</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>268912</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>237532</t>
+          <t>238911</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>334467</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>386100</t>
+          <t>385319</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>122191</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23507</t>
+          <t>23693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>43232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>65853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27836</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46815</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38839</t>
+          <t>39541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>56490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80832</t>
+          <t>81117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>18645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>39808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26494</t>
+          <t>26897</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48855</t>
+          <t>47840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57652</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>77992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46649</t>
+          <t>46220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92873</t>
+          <t>93964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119682</t>
+          <t>119792</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>27926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>53441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27855</t>
+          <t>29218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59513</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>18817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36714</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71053</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>21647</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21132</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>46859</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17416</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32906</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55854</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36382</t>
+          <t>35780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55921</t>
+          <t>57553</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76990</t>
+          <t>77839</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>106412</t>
+          <t>105766</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>65499</t>
+          <t>64726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>74434</t>
+          <t>74623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104234</t>
+          <t>103763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,37%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>64320</t>
+          <t>63506</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>83945</t>
+          <t>84943</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>113364</t>
+          <t>113023</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,97%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44051</t>
+          <t>43861</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>66373</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>70977</t>
+          <t>70966</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>99312</t>
+          <t>100141</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>265488</t>
+          <t>264725</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>246045</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>428935</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>497483</t>
+          <t>495545</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>273722</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>325611</t>
+          <t>326506</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>463343</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>534896</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>101872</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>173376</t>
+          <t>171650</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47544</t>
+          <t>47177</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>25784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46424</t>
+          <t>46737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>68335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>872</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41495</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>58122</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>45689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28775</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45386</t>
+          <t>45112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69140</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>26393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28215</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45431</t>
+          <t>45604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69331</t>
+          <t>70496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24966</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>21712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41613</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>832</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42658</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57405</t>
+          <t>57726</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17043</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>33152</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>32797</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47611</t>
+          <t>48296</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32071</t>
+          <t>32459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>33640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24575</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43572</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>38410</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>51656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76401</t>
+          <t>75134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>36107</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43637</t>
+          <t>42106</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24052</t>
+          <t>24663</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43878</t>
+          <t>44128</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>52609</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>80392</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>52995</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75126</t>
+          <t>75383</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>69827</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>107786</t>
+          <t>108015</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>138953</t>
+          <t>137895</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8214</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27785</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>111111</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>153223</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>144340</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>228457</t>
+          <t>227844</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>285309</t>
+          <t>282334</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>250610</t>
+          <t>249457</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>296246</t>
+          <t>296038</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>188183</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>228262</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>446226</t>
+          <t>449474</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>507467</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114770</t>
+          <t>114282</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>186144</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
